--- a/Параметри_Паспорт_майстер.xlsx
+++ b/Параметри_Паспорт_майстер.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -644,10 +644,6 @@
           <t>ПЕРЕКЛАД — тариф за зірковістю (чистими, грн/1000 знаків)</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -747,10 +743,6 @@
           <t>РЕДАГУВАННЯ — тариф за складністю (чистими, грн/1000 знаків)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -800,10 +792,6 @@
           <t>ФОРМАТИ — сторінковість і друк блоку</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -875,10 +863,6 @@
           <t>КОЛЬОРОВИЙ ЗРІЗ — ціна за одиницю (не залежить від накладу)</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -922,10 +906,6 @@
           <t>ОБКЛАДИНКА — ціна за одиницю (база T3), формат × ефект</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1067,10 +1047,6 @@
           <t>ТИРИ — коефіцієнт k від накладу (для блоку й обкладинки)</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -1190,10 +1166,6 @@
           <t>ЗАГАЛЬНІ — коефіцієнти та податкові ставки</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -1342,6 +1314,150 @@
       <c r="C57" s="8" t="inlineStr">
         <is>
           <t>згори на тіло, лише ДП</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>КАНАЛЬНИЙ МІКС — B2B/B2C/Ecomm, знижки й операційка каналів</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Значення</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Опис</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Частка B2B</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>% відвантаженого тиражу — гурт/дистрибуція</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Частка B2C</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>% відвантаженого тиражу — власна мережа магазинів</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Частка Ecomm</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>% відвантаженого тиражу — власний інтернет-магазин</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Знижка B2B</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>реальна зовнішня знижка, гроші повністю покидають компанію</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Споживча знижка B2C</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>РРЦ → фактична ціна продажу; ПЛЕЙСХОЛДЕР — уточнити в маркетингу</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Операційні витрати B2C</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>оренда+персонал+логістика в точки, % від фактичної ціни</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Споживча знижка Ecomm</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>РРЦ → фактична ціна продажу; ПЛЕЙСХОЛДЕР — уточнити в маркетингу</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Операційні витрати Ecomm</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>платформа+еквайринг+доставка+маркетинг+повернення</t>
         </is>
       </c>
     </row>
